--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3038,6 +3038,216 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -3076,49 +3076,49 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:07</t>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>S38/2026</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:07</t>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -3160,49 +3160,49 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:07</t>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>S38/2026</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:07</t>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:07</t>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3248,6 +3248,216 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -3286,49 +3286,49 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09</t>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>S39/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21 16:09</t>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -3370,49 +3370,49 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09</t>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>S39/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21 16:09</t>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09</t>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3458,6 +3458,216 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -3496,49 +3496,49 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>S40/2026</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28 17:55</t>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -3580,49 +3580,49 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>S40/2026</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28 17:55</t>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3471,12 +3471,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -3639,12 +3639,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3668,6 +3668,216 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -3706,49 +3706,49 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:00</t>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>S41/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05 19:00</t>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -3790,49 +3790,49 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:00</t>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>S41/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05 19:00</t>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:00</t>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3878,6 +3878,216 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -3916,49 +3916,49 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 19:34</t>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>S42/2026</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12 19:34</t>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -4000,49 +4000,49 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 19:34</t>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>S42/2026</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12 19:34</t>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 19:34</t>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4088,6 +4088,216 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -4126,49 +4126,49 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 16:47</t>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>S43/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19 16:47</t>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -4210,49 +4210,49 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 16:47</t>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>S43/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19 16:47</t>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 16:47</t>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4298,6 +4298,216 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -4336,49 +4336,49 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 16:26</t>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>S44/2026</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>26/10/2026</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26 16:26</t>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
@@ -4420,49 +4420,49 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 16:26</t>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>S44/2026</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>26/10/2026</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26 16:26</t>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 16:26</t>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_detalhadas.xlsx
+++ b/instagram-metrics/base_interacoes_detalhadas.xlsx
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
